--- a/code/inspectionTemplates.xlsx
+++ b/code/inspectionTemplates.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5595A0-309F-469B-99A7-AD592712B4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289F4BC0-5127-42E5-90D0-D6E983F05CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,8 +11,8 @@
     <sheet name="外围检测-masterdrive" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$R$39</definedName>
-    <definedName name="Z_A814C86E_25A4_42E3_B299_227C8A9779F4_.wvu.FilterData" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$Q$39</definedName>
+    <definedName name="Z_A814C86E_25A4_42E3_B299_227C8A9779F4_.wvu.FilterData" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="115">
   <si>
     <t>权重</t>
   </si>
@@ -306,15 +306,6 @@
   </si>
   <si>
     <t>操作指导</t>
-  </si>
-  <si>
-    <t>量电气室湿度。
-确认机柜内是否有凝露。</t>
-  </si>
-  <si>
-    <t>观察机柜内的粉尘程度。
-检查粉尘导电性。
-检查现场是否有针对粉尘的有效防护措施。</t>
   </si>
   <si>
     <t>观察柜体安装是否平稳
@@ -323,10 +314,6 @@
 检查柜顶是否有防异物坠落措施</t>
   </si>
   <si>
-    <t>检查通风孔是否有滤棉
-检查通风孔滤棉是否洁净</t>
-  </si>
-  <si>
     <t>检查所有装置接地端子是否有可靠接地，比如接地线截面####要求同接地线线径 。
 变频器及其出线应与敏感设备或电缆的距离不得小于20cm</t>
   </si>
@@ -338,12 +325,6 @@
     <t>规则类型</t>
   </si>
   <si>
-    <t>参数1</t>
-  </si>
-  <si>
-    <t>参数2</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -425,6 +406,31 @@
   </si>
   <si>
     <t>{"max": 50,"min": 5}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查粉尘导电性。</t>
+  </si>
+  <si>
+    <t>检查现场是否有针对粉尘的有效防护措施。</t>
+  </si>
+  <si>
+    <t>观察机柜内的粉尘程度。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">检查通风孔是否有滤棉
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查通风孔滤棉是否洁净</t>
+  </si>
+  <si>
+    <t>确认机柜内是否有凝露。</t>
+  </si>
+  <si>
+    <t>量电气室湿度。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1027,7 +1033,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -1038,16 +1044,18 @@
     <col min="6" max="6" width="9.875" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="52.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="15.625" customWidth="1"/>
-    <col min="13" max="18" width="12.25" customWidth="1"/>
-    <col min="19" max="19" width="15.375" customWidth="1"/>
-    <col min="20" max="20" width="22.25" customWidth="1"/>
+    <col min="9" max="9" width="52.25" customWidth="1"/>
+    <col min="10" max="10" width="40.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="14" width="12.25" customWidth="1"/>
+    <col min="15" max="15" width="16.125" customWidth="1"/>
+    <col min="16" max="16" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" customWidth="1"/>
+    <col min="18" max="18" width="15.375" customWidth="1"/>
+    <col min="19" max="19" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>76</v>
       </c>
@@ -1067,43 +1075,38 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
@@ -1117,24 +1120,23 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" ht="29.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="8" t="s">
@@ -1144,24 +1146,23 @@
         <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="8"/>
@@ -1169,22 +1170,23 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" ht="56.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="8" t="s">
@@ -1194,24 +1196,23 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="8"/>
@@ -1219,22 +1220,23 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="8"/>
@@ -1242,22 +1244,23 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="8" t="s">
@@ -1267,24 +1270,23 @@
         <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:18" ht="29.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:17" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
@@ -1294,24 +1296,23 @@
         <v>18</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" ht="56.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:17" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
         <v>19</v>
@@ -1323,24 +1324,23 @@
         <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="14"/>
       <c r="C11" s="8"/>
@@ -1348,22 +1348,21 @@
         <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="14"/>
       <c r="C12" s="8"/>
@@ -1371,22 +1370,21 @@
         <v>23</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="14"/>
       <c r="C13" s="8"/>
@@ -1394,22 +1392,21 @@
         <v>24</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:18" ht="29.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="8" t="s">
@@ -1419,24 +1416,23 @@
         <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="8"/>
@@ -1444,22 +1440,23 @@
         <v>27</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="8" t="s">
@@ -1469,24 +1466,23 @@
         <v>30</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" ht="29.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="8" t="s">
@@ -1496,24 +1492,23 @@
         <v>18</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
         <v>31</v>
@@ -1525,24 +1520,23 @@
         <v>34</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="14"/>
       <c r="C19" s="8"/>
@@ -1550,22 +1544,21 @@
         <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" ht="29.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="14"/>
       <c r="C20" s="8"/>
@@ -1573,22 +1566,21 @@
         <v>36</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="29.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="8" t="s">
@@ -1598,24 +1590,23 @@
         <v>39</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="69.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:10" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="8" t="s">
@@ -1625,24 +1616,23 @@
         <v>41</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" ht="29.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="8"/>
@@ -1650,22 +1640,21 @@
         <v>42</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" ht="29.25" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>43</v>
       </c>
@@ -1679,22 +1668,21 @@
         <v>46</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2"/>
-      <c r="I24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I24" s="2"/>
+      <c r="J24" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="8" t="s">
@@ -1704,22 +1692,21 @@
         <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="2"/>
+      <c r="J25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="8"/>
@@ -1727,20 +1714,19 @@
         <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="8"/>
@@ -1748,20 +1734,19 @@
         <v>51</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H27" s="2"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="8"/>
@@ -1769,20 +1754,19 @@
         <v>52</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H28" s="2"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="8" t="s">
@@ -1792,24 +1776,23 @@
         <v>55</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>56</v>
       </c>
@@ -1823,22 +1806,21 @@
         <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2"/>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="2"/>
+      <c r="J30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="8"/>
@@ -1846,20 +1828,19 @@
         <v>61</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="8"/>
@@ -1867,20 +1848,19 @@
         <v>62</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H32" s="2"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="8"/>
@@ -1888,20 +1868,19 @@
         <v>63</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="8"/>
@@ -1909,20 +1888,19 @@
         <v>64</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H34" s="2"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="8" t="s">
@@ -1932,22 +1910,21 @@
         <v>67</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="2"/>
+      <c r="J35" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="8"/>
@@ -1955,22 +1932,21 @@
         <v>68</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I36" s="3"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="8" t="s">
@@ -1980,45 +1956,43 @@
         <v>71</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H37" s="2"/>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2"/>
+      <c r="J37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="8"/>
       <c r="D38" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I38" s="2"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="8"/>
@@ -2026,33 +2000,32 @@
         <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I39" s="3"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="C40" s="10"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R39" xr:uid="{EDDA9DC0-A9A1-4E98-A384-5F40C27BBD8F}"/>
+  <autoFilter ref="A1:Q39" xr:uid="{EDDA9DC0-A9A1-4E98-A384-5F40C27BBD8F}"/>
   <customSheetViews>
     <customSheetView guid="{A814C86E-25A4-42E3-B299-227C8A9779F4}" showGridLines="0" showAutoFilter="1">
       <selection activeCell="I13" sqref="I13"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A2:G39" xr:uid="{4C4D305C-BF62-4E03-816A-792EE10B4B07}"/>
+      <autoFilter ref="A2:G39" xr:uid="{7B3CF6A9-F479-457E-8AC2-D4F8E989CF19}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2108,6 +2081,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6bd1f968-35b2-42cf-8f7c-e2953acad71e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E5923152C64AB245A4920FAC4BFBAFBF" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a147ce5196179442ab1c9726cb178aa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bd1f968-35b2-42cf-8f7c-e2953acad71e" xmlns:ns3="1ae5cbaf-126a-426e-8f85-663306326d36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10ccb65649512309cf78050fc0bef035" ns2:_="" ns3:_="">
     <xsd:import namespace="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
@@ -2330,26 +2322,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753FB6B0-EC8C-4605-AEA4-EF118B5D529E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6bd1f968-35b2-42cf-8f7c-e2953acad71e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1E602C-36E4-4A9E-B578-89D4EC443FF4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A114E3-96D0-451C-8C43-F23091AF9E6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2368,24 +2359,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1E602C-36E4-4A9E-B578-89D4EC443FF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753FB6B0-EC8C-4605-AEA4-EF118B5D529E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/code/inspectionTemplates.xlsx
+++ b/code/inspectionTemplates.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289F4BC0-5127-42E5-90D0-D6E983F05CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06744A78-5AF1-47B3-BF38-34321E621A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="外围检测-masterdrive" sheetId="6" r:id="rId1"/>
+    <sheet name="映射表" sheetId="7" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$N$39</definedName>
     <definedName name="Z_A814C86E_25A4_42E3_B299_227C8A9779F4_.wvu.FilterData" localSheetId="0" hidden="1">'外围检测-masterdrive'!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -69,10 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="115">
-  <si>
-    <t>权重</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="120">
   <si>
     <t>电气室</t>
   </si>
@@ -102,9 +100,6 @@
   </si>
   <si>
     <t>柜内是否有大量粉尘</t>
-  </si>
-  <si>
-    <t>粉尘是否导电</t>
   </si>
   <si>
     <t>是否有对粉尘的有效防护</t>
@@ -325,15 +320,6 @@
     <t>规则类型</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Mediun</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>建议规则</t>
   </si>
   <si>
@@ -341,15 +327,6 @@
   </si>
   <si>
     <t>隐患内容</t>
-  </si>
-  <si>
-    <t>再检测 -Yes</t>
-  </si>
-  <si>
-    <t>再检测项目</t>
-  </si>
-  <si>
-    <t>处理隐患</t>
   </si>
   <si>
     <t>维护说明</t>
@@ -431,6 +408,54 @@
   </si>
   <si>
     <t>量电气室湿度。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>value_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rule_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>是否必填</t>
+  </si>
+  <si>
+    <t>是否必填</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜内是否有大量粉尘=是</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉尘是否导电</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜内是否有大量粉尘=是 And 粉尘是否导电=是</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示条件</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -438,7 +463,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +490,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -565,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -590,6 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1033,7 +1067,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -1041,991 +1075,3459 @@
     <col min="3" max="3" width="14.125" customWidth="1"/>
     <col min="4" max="4" width="33.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.75" customWidth="1"/>
-    <col min="6" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.25" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.375" customWidth="1"/>
     <col min="10" max="10" width="40.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.625" customWidth="1"/>
     <col min="12" max="14" width="12.25" customWidth="1"/>
-    <col min="15" max="15" width="16.125" customWidth="1"/>
-    <col min="16" max="16" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.25" customWidth="1"/>
-    <col min="18" max="18" width="15.375" customWidth="1"/>
-    <col min="19" max="19" width="22.25" customWidth="1"/>
+    <col min="15" max="15" width="15.375" customWidth="1"/>
+    <col min="16" max="16" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="K1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K1" s="6" t="s">
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E2, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>number_range</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>94</v>
+      <c r="H2" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>93</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E3, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>number_range</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="8"/>
       <c r="D4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E4, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E5, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="8"/>
       <c r="D6" s="15" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E6, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="J6" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="8"/>
       <c r="D7" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E7, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="J7" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E8, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="29.25" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E9, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="56.25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E10, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="14"/>
       <c r="C11" s="8"/>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E11, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="14"/>
       <c r="C12" s="8"/>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E12, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="14"/>
       <c r="C13" s="8"/>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E13, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" ht="29.25" x14ac:dyDescent="0.3">
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E14, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="8"/>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E15, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E16, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E17, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E18, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="14"/>
       <c r="C19" s="8"/>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E19, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="14"/>
       <c r="C20" s="8"/>
       <c r="D20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F20" s="16" t="str">
+        <f>IFERROR(VLOOKUP(E20, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E21, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="56.25" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E22, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="8"/>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E23, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" ht="29.25" x14ac:dyDescent="0.3">
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" ht="29.25" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="D24" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E24, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E25, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="8"/>
       <c r="D26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H26" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E26, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="8"/>
       <c r="D27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E27, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="8"/>
       <c r="D28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E28, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E29, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="B30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E30, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="8"/>
       <c r="D31" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H31" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E31, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
-    </row>
-    <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="8"/>
       <c r="D32" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E32, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="8"/>
       <c r="D33" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E33, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="8"/>
       <c r="D34" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E34, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="3"/>
-    </row>
-    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E35, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>text_pattern</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I35" s="2"/>
       <c r="J35" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="8"/>
       <c r="D36" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E36, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E37, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>number_range</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="I37" s="2"/>
       <c r="J37" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="8"/>
       <c r="D38" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E38, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>enum</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="3"/>
-    </row>
-    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="8"/>
       <c r="D39" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f>IFERROR(VLOOKUP(E39, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v>boolean_equal</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="C40" s="10"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="F40" t="str">
+        <f>IFERROR(VLOOKUP(E40, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F41" t="str">
+        <f>IFERROR(VLOOKUP(E41, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F42" t="str">
+        <f>IFERROR(VLOOKUP(E42, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F43" t="str">
+        <f>IFERROR(VLOOKUP(E43, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F44" t="str">
+        <f>IFERROR(VLOOKUP(E44, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F45" t="str">
+        <f>IFERROR(VLOOKUP(E45, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F46" t="str">
+        <f>IFERROR(VLOOKUP(E46, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F47" t="str">
+        <f>IFERROR(VLOOKUP(E47, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="F48" t="str">
+        <f>IFERROR(VLOOKUP(E48, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F49" t="str">
+        <f>IFERROR(VLOOKUP(E49, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F50" t="str">
+        <f>IFERROR(VLOOKUP(E50, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F51" t="str">
+        <f>IFERROR(VLOOKUP(E51, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F52" t="str">
+        <f>IFERROR(VLOOKUP(E52, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F53" t="str">
+        <f>IFERROR(VLOOKUP(E53, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F54" t="str">
+        <f>IFERROR(VLOOKUP(E54, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F55" t="str">
+        <f>IFERROR(VLOOKUP(E55, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F56" t="str">
+        <f>IFERROR(VLOOKUP(E56, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F57" t="str">
+        <f>IFERROR(VLOOKUP(E57, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F58" t="str">
+        <f>IFERROR(VLOOKUP(E58, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F59" t="str">
+        <f>IFERROR(VLOOKUP(E59, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F60" t="str">
+        <f>IFERROR(VLOOKUP(E60, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F61" t="str">
+        <f>IFERROR(VLOOKUP(E61, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F62" t="str">
+        <f>IFERROR(VLOOKUP(E62, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F63" t="str">
+        <f>IFERROR(VLOOKUP(E63, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F64" t="str">
+        <f>IFERROR(VLOOKUP(E64, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F65" t="str">
+        <f>IFERROR(VLOOKUP(E65, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F66" t="str">
+        <f>IFERROR(VLOOKUP(E66, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F67" t="str">
+        <f>IFERROR(VLOOKUP(E67, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F68" t="str">
+        <f>IFERROR(VLOOKUP(E68, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F69" t="str">
+        <f>IFERROR(VLOOKUP(E69, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F70" t="str">
+        <f>IFERROR(VLOOKUP(E70, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F71" t="str">
+        <f>IFERROR(VLOOKUP(E71, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F72" t="str">
+        <f>IFERROR(VLOOKUP(E72, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F73" t="str">
+        <f>IFERROR(VLOOKUP(E73, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F74" t="str">
+        <f>IFERROR(VLOOKUP(E74, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F75" t="str">
+        <f>IFERROR(VLOOKUP(E75, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F76" t="str">
+        <f>IFERROR(VLOOKUP(E76, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F77" t="str">
+        <f>IFERROR(VLOOKUP(E77, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F78" t="str">
+        <f>IFERROR(VLOOKUP(E78, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F79" t="str">
+        <f>IFERROR(VLOOKUP(E79, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F80" t="str">
+        <f>IFERROR(VLOOKUP(E80, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F81" t="str">
+        <f>IFERROR(VLOOKUP(E81, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F82" t="str">
+        <f>IFERROR(VLOOKUP(E82, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F83" t="str">
+        <f>IFERROR(VLOOKUP(E83, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F84" t="str">
+        <f>IFERROR(VLOOKUP(E84, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F85" t="str">
+        <f>IFERROR(VLOOKUP(E85, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F86" t="str">
+        <f>IFERROR(VLOOKUP(E86, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F87" t="str">
+        <f>IFERROR(VLOOKUP(E87, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F88" t="str">
+        <f>IFERROR(VLOOKUP(E88, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F89" t="str">
+        <f>IFERROR(VLOOKUP(E89, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F90" t="str">
+        <f>IFERROR(VLOOKUP(E90, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F91" t="str">
+        <f>IFERROR(VLOOKUP(E91, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F92" t="str">
+        <f>IFERROR(VLOOKUP(E92, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F93" t="str">
+        <f>IFERROR(VLOOKUP(E93, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F94" t="str">
+        <f>IFERROR(VLOOKUP(E94, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F95" t="str">
+        <f>IFERROR(VLOOKUP(E95, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F96" t="str">
+        <f>IFERROR(VLOOKUP(E96, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F97" t="str">
+        <f>IFERROR(VLOOKUP(E97, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F98" t="str">
+        <f>IFERROR(VLOOKUP(E98, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F99" t="str">
+        <f>IFERROR(VLOOKUP(E99, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F100" t="str">
+        <f>IFERROR(VLOOKUP(E100, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F101" t="str">
+        <f>IFERROR(VLOOKUP(E101, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F102" t="str">
+        <f>IFERROR(VLOOKUP(E102, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F103" t="str">
+        <f>IFERROR(VLOOKUP(E103, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F104" t="str">
+        <f>IFERROR(VLOOKUP(E104, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F105" t="str">
+        <f>IFERROR(VLOOKUP(E105, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F106" t="str">
+        <f>IFERROR(VLOOKUP(E106, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F107" t="str">
+        <f>IFERROR(VLOOKUP(E107, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F108" t="str">
+        <f>IFERROR(VLOOKUP(E108, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F109" t="str">
+        <f>IFERROR(VLOOKUP(E109, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F110" t="str">
+        <f>IFERROR(VLOOKUP(E110, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F111" t="str">
+        <f>IFERROR(VLOOKUP(E111, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F112" t="str">
+        <f>IFERROR(VLOOKUP(E112, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F113" t="str">
+        <f>IFERROR(VLOOKUP(E113, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F114" t="str">
+        <f>IFERROR(VLOOKUP(E114, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F115" t="str">
+        <f>IFERROR(VLOOKUP(E115, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F116" t="str">
+        <f>IFERROR(VLOOKUP(E116, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F117" t="str">
+        <f>IFERROR(VLOOKUP(E117, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F118" t="str">
+        <f>IFERROR(VLOOKUP(E118, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F119" t="str">
+        <f>IFERROR(VLOOKUP(E119, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F120" t="str">
+        <f>IFERROR(VLOOKUP(E120, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F121" t="str">
+        <f>IFERROR(VLOOKUP(E121, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F122" t="str">
+        <f>IFERROR(VLOOKUP(E122, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F123" t="str">
+        <f>IFERROR(VLOOKUP(E123, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F124" t="str">
+        <f>IFERROR(VLOOKUP(E124, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F125" t="str">
+        <f>IFERROR(VLOOKUP(E125, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F126" t="str">
+        <f>IFERROR(VLOOKUP(E126, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F127" t="str">
+        <f>IFERROR(VLOOKUP(E127, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F128" t="str">
+        <f>IFERROR(VLOOKUP(E128, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F129" t="str">
+        <f>IFERROR(VLOOKUP(E129, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F130" t="str">
+        <f>IFERROR(VLOOKUP(E130, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F131" t="str">
+        <f>IFERROR(VLOOKUP(E131, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F132" t="str">
+        <f>IFERROR(VLOOKUP(E132, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F133" t="str">
+        <f>IFERROR(VLOOKUP(E133, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F134" t="str">
+        <f>IFERROR(VLOOKUP(E134, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F135" t="str">
+        <f>IFERROR(VLOOKUP(E135, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F136" t="str">
+        <f>IFERROR(VLOOKUP(E136, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F137" t="str">
+        <f>IFERROR(VLOOKUP(E137, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F138" t="str">
+        <f>IFERROR(VLOOKUP(E138, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F139" t="str">
+        <f>IFERROR(VLOOKUP(E139, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F140" t="str">
+        <f>IFERROR(VLOOKUP(E140, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F141" t="str">
+        <f>IFERROR(VLOOKUP(E141, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F142" t="str">
+        <f>IFERROR(VLOOKUP(E142, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F143" t="str">
+        <f>IFERROR(VLOOKUP(E143, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F144" t="str">
+        <f>IFERROR(VLOOKUP(E144, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F145" t="str">
+        <f>IFERROR(VLOOKUP(E145, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F146" t="str">
+        <f>IFERROR(VLOOKUP(E146, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F147" t="str">
+        <f>IFERROR(VLOOKUP(E147, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F148" t="str">
+        <f>IFERROR(VLOOKUP(E148, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F149" t="str">
+        <f>IFERROR(VLOOKUP(E149, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F150" t="str">
+        <f>IFERROR(VLOOKUP(E150, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F151" t="str">
+        <f>IFERROR(VLOOKUP(E151, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F152" t="str">
+        <f>IFERROR(VLOOKUP(E152, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F153" t="str">
+        <f>IFERROR(VLOOKUP(E153, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F154" t="str">
+        <f>IFERROR(VLOOKUP(E154, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F155" t="str">
+        <f>IFERROR(VLOOKUP(E155, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F156" t="str">
+        <f>IFERROR(VLOOKUP(E156, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F157" t="str">
+        <f>IFERROR(VLOOKUP(E157, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F158" t="str">
+        <f>IFERROR(VLOOKUP(E158, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F159" t="str">
+        <f>IFERROR(VLOOKUP(E159, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F160" t="str">
+        <f>IFERROR(VLOOKUP(E160, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F161" t="str">
+        <f>IFERROR(VLOOKUP(E161, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F162" t="str">
+        <f>IFERROR(VLOOKUP(E162, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F163" t="str">
+        <f>IFERROR(VLOOKUP(E163, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F164" t="str">
+        <f>IFERROR(VLOOKUP(E164, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F165" t="str">
+        <f>IFERROR(VLOOKUP(E165, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F166" t="str">
+        <f>IFERROR(VLOOKUP(E166, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F167" t="str">
+        <f>IFERROR(VLOOKUP(E167, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F168" t="str">
+        <f>IFERROR(VLOOKUP(E168, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F169" t="str">
+        <f>IFERROR(VLOOKUP(E169, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F170" t="str">
+        <f>IFERROR(VLOOKUP(E170, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F171" t="str">
+        <f>IFERROR(VLOOKUP(E171, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F172" t="str">
+        <f>IFERROR(VLOOKUP(E172, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F173" t="str">
+        <f>IFERROR(VLOOKUP(E173, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F174" t="str">
+        <f>IFERROR(VLOOKUP(E174, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F175" t="str">
+        <f>IFERROR(VLOOKUP(E175, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F176" t="str">
+        <f>IFERROR(VLOOKUP(E176, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F177" t="str">
+        <f>IFERROR(VLOOKUP(E177, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F178" t="str">
+        <f>IFERROR(VLOOKUP(E178, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F179" t="str">
+        <f>IFERROR(VLOOKUP(E179, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F180" t="str">
+        <f>IFERROR(VLOOKUP(E180, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F181" t="str">
+        <f>IFERROR(VLOOKUP(E181, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F182" t="str">
+        <f>IFERROR(VLOOKUP(E182, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F183" t="str">
+        <f>IFERROR(VLOOKUP(E183, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F184" t="str">
+        <f>IFERROR(VLOOKUP(E184, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F185" t="str">
+        <f>IFERROR(VLOOKUP(E185, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F186" t="str">
+        <f>IFERROR(VLOOKUP(E186, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F187" t="str">
+        <f>IFERROR(VLOOKUP(E187, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F188" t="str">
+        <f>IFERROR(VLOOKUP(E188, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F189" t="str">
+        <f>IFERROR(VLOOKUP(E189, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F190" t="str">
+        <f>IFERROR(VLOOKUP(E190, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F191" t="str">
+        <f>IFERROR(VLOOKUP(E191, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F192" t="str">
+        <f>IFERROR(VLOOKUP(E192, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F193" t="str">
+        <f>IFERROR(VLOOKUP(E193, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F194" t="str">
+        <f>IFERROR(VLOOKUP(E194, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F195" t="str">
+        <f>IFERROR(VLOOKUP(E195, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F196" t="str">
+        <f>IFERROR(VLOOKUP(E196, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F197" t="str">
+        <f>IFERROR(VLOOKUP(E197, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F198" t="str">
+        <f>IFERROR(VLOOKUP(E198, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F199" t="str">
+        <f>IFERROR(VLOOKUP(E199, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F200" t="str">
+        <f>IFERROR(VLOOKUP(E200, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F201" t="str">
+        <f>IFERROR(VLOOKUP(E201, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F202" t="str">
+        <f>IFERROR(VLOOKUP(E202, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F203" t="str">
+        <f>IFERROR(VLOOKUP(E203, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F204" t="str">
+        <f>IFERROR(VLOOKUP(E204, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F205" t="str">
+        <f>IFERROR(VLOOKUP(E205, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F206" t="str">
+        <f>IFERROR(VLOOKUP(E206, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F207" t="str">
+        <f>IFERROR(VLOOKUP(E207, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F208" t="str">
+        <f>IFERROR(VLOOKUP(E208, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F209" t="str">
+        <f>IFERROR(VLOOKUP(E209, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F210" t="str">
+        <f>IFERROR(VLOOKUP(E210, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F211" t="str">
+        <f>IFERROR(VLOOKUP(E211, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F212" t="str">
+        <f>IFERROR(VLOOKUP(E212, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F213" t="str">
+        <f>IFERROR(VLOOKUP(E213, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F214" t="str">
+        <f>IFERROR(VLOOKUP(E214, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F215" t="str">
+        <f>IFERROR(VLOOKUP(E215, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F216" t="str">
+        <f>IFERROR(VLOOKUP(E216, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F217" t="str">
+        <f>IFERROR(VLOOKUP(E217, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F218" t="str">
+        <f>IFERROR(VLOOKUP(E218, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F219" t="str">
+        <f>IFERROR(VLOOKUP(E219, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F220" t="str">
+        <f>IFERROR(VLOOKUP(E220, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F221" t="str">
+        <f>IFERROR(VLOOKUP(E221, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F222" t="str">
+        <f>IFERROR(VLOOKUP(E222, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F223" t="str">
+        <f>IFERROR(VLOOKUP(E223, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F224" t="str">
+        <f>IFERROR(VLOOKUP(E224, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F225" t="str">
+        <f>IFERROR(VLOOKUP(E225, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F226" t="str">
+        <f>IFERROR(VLOOKUP(E226, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F227" t="str">
+        <f>IFERROR(VLOOKUP(E227, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F228" t="str">
+        <f>IFERROR(VLOOKUP(E228, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F229" t="str">
+        <f>IFERROR(VLOOKUP(E229, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F230" t="str">
+        <f>IFERROR(VLOOKUP(E230, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F231" t="str">
+        <f>IFERROR(VLOOKUP(E231, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F232" t="str">
+        <f>IFERROR(VLOOKUP(E232, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F233" t="str">
+        <f>IFERROR(VLOOKUP(E233, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F234" t="str">
+        <f>IFERROR(VLOOKUP(E234, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F235" t="str">
+        <f>IFERROR(VLOOKUP(E235, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F236" t="str">
+        <f>IFERROR(VLOOKUP(E236, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F237" t="str">
+        <f>IFERROR(VLOOKUP(E237, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F238" t="str">
+        <f>IFERROR(VLOOKUP(E238, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F239" t="str">
+        <f>IFERROR(VLOOKUP(E239, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F240" t="str">
+        <f>IFERROR(VLOOKUP(E240, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F241" t="str">
+        <f>IFERROR(VLOOKUP(E241, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F242" t="str">
+        <f>IFERROR(VLOOKUP(E242, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F243" t="str">
+        <f>IFERROR(VLOOKUP(E243, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F244" t="str">
+        <f>IFERROR(VLOOKUP(E244, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F245" t="str">
+        <f>IFERROR(VLOOKUP(E245, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F246" t="str">
+        <f>IFERROR(VLOOKUP(E246, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F247" t="str">
+        <f>IFERROR(VLOOKUP(E247, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F248" t="str">
+        <f>IFERROR(VLOOKUP(E248, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F249" t="str">
+        <f>IFERROR(VLOOKUP(E249, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F250" t="str">
+        <f>IFERROR(VLOOKUP(E250, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F251" t="str">
+        <f>IFERROR(VLOOKUP(E251, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F252" t="str">
+        <f>IFERROR(VLOOKUP(E252, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F253" t="str">
+        <f>IFERROR(VLOOKUP(E253, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F254" t="str">
+        <f>IFERROR(VLOOKUP(E254, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F255" t="str">
+        <f>IFERROR(VLOOKUP(E255, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F256" t="str">
+        <f>IFERROR(VLOOKUP(E256, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F257" t="str">
+        <f>IFERROR(VLOOKUP(E257, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F258" t="str">
+        <f>IFERROR(VLOOKUP(E258, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F259" t="str">
+        <f>IFERROR(VLOOKUP(E259, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F260" t="str">
+        <f>IFERROR(VLOOKUP(E260, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F261" t="str">
+        <f>IFERROR(VLOOKUP(E261, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F262" t="str">
+        <f>IFERROR(VLOOKUP(E262, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F263" t="str">
+        <f>IFERROR(VLOOKUP(E263, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F264" t="str">
+        <f>IFERROR(VLOOKUP(E264, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F265" t="str">
+        <f>IFERROR(VLOOKUP(E265, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F266" t="str">
+        <f>IFERROR(VLOOKUP(E266, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F267" t="str">
+        <f>IFERROR(VLOOKUP(E267, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F268" t="str">
+        <f>IFERROR(VLOOKUP(E268, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F269" t="str">
+        <f>IFERROR(VLOOKUP(E269, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F270" t="str">
+        <f>IFERROR(VLOOKUP(E270, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F271" t="str">
+        <f>IFERROR(VLOOKUP(E271, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F272" t="str">
+        <f>IFERROR(VLOOKUP(E272, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F273" t="str">
+        <f>IFERROR(VLOOKUP(E273, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F274" t="str">
+        <f>IFERROR(VLOOKUP(E274, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F275" t="str">
+        <f>IFERROR(VLOOKUP(E275, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F276" t="str">
+        <f>IFERROR(VLOOKUP(E276, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F277" t="str">
+        <f>IFERROR(VLOOKUP(E277, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F278" t="str">
+        <f>IFERROR(VLOOKUP(E278, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F279" t="str">
+        <f>IFERROR(VLOOKUP(E279, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F280" t="str">
+        <f>IFERROR(VLOOKUP(E280, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F281" t="str">
+        <f>IFERROR(VLOOKUP(E281, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F282" t="str">
+        <f>IFERROR(VLOOKUP(E282, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F283" t="str">
+        <f>IFERROR(VLOOKUP(E283, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F284" t="str">
+        <f>IFERROR(VLOOKUP(E284, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F285" t="str">
+        <f>IFERROR(VLOOKUP(E285, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F286" t="str">
+        <f>IFERROR(VLOOKUP(E286, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F287" t="str">
+        <f>IFERROR(VLOOKUP(E287, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F288" t="str">
+        <f>IFERROR(VLOOKUP(E288, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F289" t="str">
+        <f>IFERROR(VLOOKUP(E289, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F290" t="str">
+        <f>IFERROR(VLOOKUP(E290, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F291" t="str">
+        <f>IFERROR(VLOOKUP(E291, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F292" t="str">
+        <f>IFERROR(VLOOKUP(E292, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F293" t="str">
+        <f>IFERROR(VLOOKUP(E293, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F294" t="str">
+        <f>IFERROR(VLOOKUP(E294, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F295" t="str">
+        <f>IFERROR(VLOOKUP(E295, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F296" t="str">
+        <f>IFERROR(VLOOKUP(E296, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F297" t="str">
+        <f>IFERROR(VLOOKUP(E297, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F298" t="str">
+        <f>IFERROR(VLOOKUP(E298, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F299" t="str">
+        <f>IFERROR(VLOOKUP(E299, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F300" t="str">
+        <f>IFERROR(VLOOKUP(E300, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F301" t="str">
+        <f>IFERROR(VLOOKUP(E301, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F302" t="str">
+        <f>IFERROR(VLOOKUP(E302, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F303" t="str">
+        <f>IFERROR(VLOOKUP(E303, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F304" t="str">
+        <f>IFERROR(VLOOKUP(E304, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F305" t="str">
+        <f>IFERROR(VLOOKUP(E305, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F306" t="str">
+        <f>IFERROR(VLOOKUP(E306, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F307" t="str">
+        <f>IFERROR(VLOOKUP(E307, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F308" t="str">
+        <f>IFERROR(VLOOKUP(E308, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F309" t="str">
+        <f>IFERROR(VLOOKUP(E309, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F310" t="str">
+        <f>IFERROR(VLOOKUP(E310, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F311" t="str">
+        <f>IFERROR(VLOOKUP(E311, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F312" t="str">
+        <f>IFERROR(VLOOKUP(E312, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F313" t="str">
+        <f>IFERROR(VLOOKUP(E313, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F314" t="str">
+        <f>IFERROR(VLOOKUP(E314, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F315" t="str">
+        <f>IFERROR(VLOOKUP(E315, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F316" t="str">
+        <f>IFERROR(VLOOKUP(E316, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F317" t="str">
+        <f>IFERROR(VLOOKUP(E317, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F318" t="str">
+        <f>IFERROR(VLOOKUP(E318, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F319" t="str">
+        <f>IFERROR(VLOOKUP(E319, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F320" t="str">
+        <f>IFERROR(VLOOKUP(E320, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F321" t="str">
+        <f>IFERROR(VLOOKUP(E321, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F322" t="str">
+        <f>IFERROR(VLOOKUP(E322, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F323" t="str">
+        <f>IFERROR(VLOOKUP(E323, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F324" t="str">
+        <f>IFERROR(VLOOKUP(E324, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F325" t="str">
+        <f>IFERROR(VLOOKUP(E325, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F326" t="str">
+        <f>IFERROR(VLOOKUP(E326, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F327" t="str">
+        <f>IFERROR(VLOOKUP(E327, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F328" t="str">
+        <f>IFERROR(VLOOKUP(E328, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F329" t="str">
+        <f>IFERROR(VLOOKUP(E329, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F330" t="str">
+        <f>IFERROR(VLOOKUP(E330, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F331" t="str">
+        <f>IFERROR(VLOOKUP(E331, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F332" t="str">
+        <f>IFERROR(VLOOKUP(E332, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F333" t="str">
+        <f>IFERROR(VLOOKUP(E333, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F334" t="str">
+        <f>IFERROR(VLOOKUP(E334, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F335" t="str">
+        <f>IFERROR(VLOOKUP(E335, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F336" t="str">
+        <f>IFERROR(VLOOKUP(E336, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F337" t="str">
+        <f>IFERROR(VLOOKUP(E337, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F338" t="str">
+        <f>IFERROR(VLOOKUP(E338, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F339" t="str">
+        <f>IFERROR(VLOOKUP(E339, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F340" t="str">
+        <f>IFERROR(VLOOKUP(E340, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F341" t="str">
+        <f>IFERROR(VLOOKUP(E341, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F342" t="str">
+        <f>IFERROR(VLOOKUP(E342, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F343" t="str">
+        <f>IFERROR(VLOOKUP(E343, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F344" t="str">
+        <f>IFERROR(VLOOKUP(E344, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F345" t="str">
+        <f>IFERROR(VLOOKUP(E345, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F346" t="str">
+        <f>IFERROR(VLOOKUP(E346, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F347" t="str">
+        <f>IFERROR(VLOOKUP(E347, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F348" t="str">
+        <f>IFERROR(VLOOKUP(E348, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F349" t="str">
+        <f>IFERROR(VLOOKUP(E349, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F350" t="str">
+        <f>IFERROR(VLOOKUP(E350, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F351" t="str">
+        <f>IFERROR(VLOOKUP(E351, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F352" t="str">
+        <f>IFERROR(VLOOKUP(E352, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F353" t="str">
+        <f>IFERROR(VLOOKUP(E353, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F354" t="str">
+        <f>IFERROR(VLOOKUP(E354, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F355" t="str">
+        <f>IFERROR(VLOOKUP(E355, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F356" t="str">
+        <f>IFERROR(VLOOKUP(E356, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F357" t="str">
+        <f>IFERROR(VLOOKUP(E357, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F358" t="str">
+        <f>IFERROR(VLOOKUP(E358, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F359" t="str">
+        <f>IFERROR(VLOOKUP(E359, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F360" t="str">
+        <f>IFERROR(VLOOKUP(E360, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F361" t="str">
+        <f>IFERROR(VLOOKUP(E361, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F362" t="str">
+        <f>IFERROR(VLOOKUP(E362, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F363" t="str">
+        <f>IFERROR(VLOOKUP(E363, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F364" t="str">
+        <f>IFERROR(VLOOKUP(E364, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F365" t="str">
+        <f>IFERROR(VLOOKUP(E365, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F366" t="str">
+        <f>IFERROR(VLOOKUP(E366, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F367" t="str">
+        <f>IFERROR(VLOOKUP(E367, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F368" t="str">
+        <f>IFERROR(VLOOKUP(E368, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F369" t="str">
+        <f>IFERROR(VLOOKUP(E369, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F370" t="str">
+        <f>IFERROR(VLOOKUP(E370, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F371" t="str">
+        <f>IFERROR(VLOOKUP(E371, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F372" t="str">
+        <f>IFERROR(VLOOKUP(E372, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F373" t="str">
+        <f>IFERROR(VLOOKUP(E373, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F374" t="str">
+        <f>IFERROR(VLOOKUP(E374, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F375" t="str">
+        <f>IFERROR(VLOOKUP(E375, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F376" t="str">
+        <f>IFERROR(VLOOKUP(E376, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F377" t="str">
+        <f>IFERROR(VLOOKUP(E377, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F378" t="str">
+        <f>IFERROR(VLOOKUP(E378, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F379" t="str">
+        <f>IFERROR(VLOOKUP(E379, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F380" t="str">
+        <f>IFERROR(VLOOKUP(E380, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F381" t="str">
+        <f>IFERROR(VLOOKUP(E381, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F382" t="str">
+        <f>IFERROR(VLOOKUP(E382, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F383" t="str">
+        <f>IFERROR(VLOOKUP(E383, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F384" t="str">
+        <f>IFERROR(VLOOKUP(E384, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F385" t="str">
+        <f>IFERROR(VLOOKUP(E385, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F386" t="str">
+        <f>IFERROR(VLOOKUP(E386, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F387" t="str">
+        <f>IFERROR(VLOOKUP(E387, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F388" t="str">
+        <f>IFERROR(VLOOKUP(E388, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F389" t="str">
+        <f>IFERROR(VLOOKUP(E389, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F390" t="str">
+        <f>IFERROR(VLOOKUP(E390, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F391" t="str">
+        <f>IFERROR(VLOOKUP(E391, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F392" t="str">
+        <f>IFERROR(VLOOKUP(E392, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F393" t="str">
+        <f>IFERROR(VLOOKUP(E393, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F394" t="str">
+        <f>IFERROR(VLOOKUP(E394, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F395" t="str">
+        <f>IFERROR(VLOOKUP(E395, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F396" t="str">
+        <f>IFERROR(VLOOKUP(E396, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F397" t="str">
+        <f>IFERROR(VLOOKUP(E397, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F398" t="str">
+        <f>IFERROR(VLOOKUP(E398, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F399" t="str">
+        <f>IFERROR(VLOOKUP(E399, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F400" t="str">
+        <f>IFERROR(VLOOKUP(E400, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="401" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F401" t="str">
+        <f>IFERROR(VLOOKUP(E401, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F402" t="str">
+        <f>IFERROR(VLOOKUP(E402, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F403" t="str">
+        <f>IFERROR(VLOOKUP(E403, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F404" t="str">
+        <f>IFERROR(VLOOKUP(E404, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F405" t="str">
+        <f>IFERROR(VLOOKUP(E405, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F406" t="str">
+        <f>IFERROR(VLOOKUP(E406, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F407" t="str">
+        <f>IFERROR(VLOOKUP(E407, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F408" t="str">
+        <f>IFERROR(VLOOKUP(E408, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="409" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F409" t="str">
+        <f>IFERROR(VLOOKUP(E409, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F410" t="str">
+        <f>IFERROR(VLOOKUP(E410, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F411" t="str">
+        <f>IFERROR(VLOOKUP(E411, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F412" t="str">
+        <f>IFERROR(VLOOKUP(E412, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F413" t="str">
+        <f>IFERROR(VLOOKUP(E413, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F414" t="str">
+        <f>IFERROR(VLOOKUP(E414, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F415" t="str">
+        <f>IFERROR(VLOOKUP(E415, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="416" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F416" t="str">
+        <f>IFERROR(VLOOKUP(E416, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F417" t="str">
+        <f>IFERROR(VLOOKUP(E417, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F418" t="str">
+        <f>IFERROR(VLOOKUP(E418, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F419" t="str">
+        <f>IFERROR(VLOOKUP(E419, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F420" t="str">
+        <f>IFERROR(VLOOKUP(E420, 映射表!$A$2:$B$5, 2, 0), "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q39" xr:uid="{EDDA9DC0-A9A1-4E98-A384-5F40C27BBD8F}"/>
+  <autoFilter ref="A1:N39" xr:uid="{EDDA9DC0-A9A1-4E98-A384-5F40C27BBD8F}"/>
   <customSheetViews>
     <customSheetView guid="{A814C86E-25A4-42E3-B299-227C8A9779F4}" showGridLines="0" showAutoFilter="1">
       <selection activeCell="I13" sqref="I13"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A2:G39" xr:uid="{7B3CF6A9-F479-457E-8AC2-D4F8E989CF19}"/>
+      <autoFilter ref="A2:G39" xr:uid="{E56D28B8-5ABD-4BD2-BD6B-078710A769B2}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2074,32 +4576,100 @@
       <formula>(#REF!=3)</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H40:H1048576" xr:uid="{C3FEBB18-1846-41F4-89B6-BEC1CF2E090B}">
+      <formula1>"是;否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{38A71751-9F4A-45A9-88C8-115B66B533DB}">
+          <x14:formula1>
+            <xm:f>映射表!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E696D328-5406-42D4-9E84-A4165F8DBA74}">
+          <x14:formula1>
+            <xm:f>映射表!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H39</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40689F83-6B69-4B07-9EA7-AD99502435C1}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6bd1f968-35b2-42cf-8f7c-e2953acad71e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E5923152C64AB245A4920FAC4BFBAFBF" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a147ce5196179442ab1c9726cb178aa9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bd1f968-35b2-42cf-8f7c-e2953acad71e" xmlns:ns3="1ae5cbaf-126a-426e-8f85-663306326d36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10ccb65649512309cf78050fc0bef035" ns2:_="" ns3:_="">
     <xsd:import namespace="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
@@ -2322,25 +4892,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753FB6B0-EC8C-4605-AEA4-EF118B5D529E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6bd1f968-35b2-42cf-8f7c-e2953acad71e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1E602C-36E4-4A9E-B578-89D4EC443FF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A114E3-96D0-451C-8C43-F23091AF9E6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2359,6 +4930,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753FB6B0-EC8C-4605-AEA4-EF118B5D529E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6bd1f968-35b2-42cf-8f7c-e2953acad71e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1E602C-36E4-4A9E-B578-89D4EC443FF4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>
